--- a/competition/專題競賽資訊.xlsx
+++ b/competition/專題競賽資訊.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yxuan/Documents/SaveMyBook/competition/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\benj1\Documents\SaveMyBook\competition\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E97525BA-6511-D841-AC77-47B43E930B86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF3AE21B-44D0-4161-9E93-FDC23F939508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="28340" windowHeight="18460" activeTab="1" xr2:uid="{285F9FD4-B296-469E-ADA7-FB304A9A05A2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{285F9FD4-B296-469E-ADA7-FB304A9A05A2}"/>
   </bookViews>
   <sheets>
     <sheet name="2025年相關競賽" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="161">
   <si>
     <t>競賽名稱</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -118,10 +118,6 @@
   </si>
   <si>
     <t>https://www.ml.vnu.edu.tw/</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025第六屆高科盃全國商業智慧競賽</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -425,7 +421,7 @@
       <rPr>
         <sz val="12"/>
         <color theme="1"/>
-        <rFont val="微軟正黑體"/>
+        <rFont val="Microsoft JhengHei"/>
         <family val="2"/>
         <charset val="136"/>
         <scheme val="minor"/>
@@ -441,7 +437,7 @@
       <rPr>
         <sz val="12"/>
         <color theme="1"/>
-        <rFont val="微軟正黑體"/>
+        <rFont val="Microsoft JhengHei"/>
         <family val="2"/>
         <charset val="136"/>
         <scheme val="minor"/>
@@ -656,14 +652,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>2026全國AI專題創意競賽</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026/9/1(二)~2026/12/1(二)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>初賽：2026/12/11(五)
 決賽：2026/12/19(六)</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -674,16 +662,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>國立臺南大學</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://bhuntr.com/tw/competitions/jnlxrqcq6vyvmq6t7t</t>
-  </si>
-  <si>
-    <t>2026 全國大專院校產學創新實作競賽</t>
-  </si>
-  <si>
     <t>https://eedept.ncue.edu.tw/innovation2026/index.html</t>
   </si>
   <si>
@@ -705,19 +683,53 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>~2026/10/22(四）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>2026全國AI專題創意競賽</t>
+  </si>
+  <si>
+    <t>https://phpweb4.nutn.edu.tw/ilt/wordpress/?page_id=4308</t>
+  </si>
+  <si>
+    <t>國立臺南大學理工學院、數位學習科技學系、電機工程學系、知識應用暨網路服務研究中心、AI 智慧技術與應用人才培訓據點</t>
+  </si>
+  <si>
+    <t>2026全國大專院校產學創新實作競賽</t>
+  </si>
+  <si>
+    <t>2026/9/1(二)~2026/12/1(二)</t>
+  </si>
+  <si>
+    <t>2026/9/1(二)~2026/10/22(四）</t>
+  </si>
+  <si>
+    <t>2025第六屆高科盃全國商業智慧競賽</t>
+  </si>
+  <si>
+    <t>第七屆高科盃全國商業智慧競賽</t>
+  </si>
+  <si>
+    <t>~2026/10/28(三）</t>
+  </si>
+  <si>
+    <t>初賽：2026/10/28(三）
+決賽：2026/11/22(日)</t>
+  </si>
+  <si>
+    <t>https://ic.dxing888.com/</t>
+  </si>
+  <si>
+    <t>初賽：書面審查
+決賽：國立高雄科技大學</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="微軟正黑體"/>
+      <name val="Microsoft JhengHei"/>
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
@@ -726,14 +738,14 @@
       <b/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="微軟正黑體"/>
+      <name val="Microsoft JhengHei"/>
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="微軟正黑體"/>
+      <name val="Microsoft JhengHei"/>
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
@@ -742,7 +754,7 @@
       <u/>
       <sz val="12"/>
       <color theme="10"/>
-      <name val="微軟正黑體"/>
+      <name val="Microsoft JhengHei"/>
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
@@ -750,7 +762,7 @@
     <font>
       <sz val="12"/>
       <color rgb="FF333333"/>
-      <name val="微軟正黑體"/>
+      <name val="Microsoft JhengHei"/>
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
@@ -758,7 +770,7 @@
     <font>
       <sz val="12"/>
       <color rgb="FF18212B"/>
-      <name val="微軟正黑體"/>
+      <name val="Microsoft JhengHei"/>
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
@@ -766,7 +778,7 @@
     <font>
       <sz val="12"/>
       <color rgb="FF212121"/>
-      <name val="微軟正黑體"/>
+      <name val="Microsoft JhengHei"/>
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
@@ -774,7 +786,16 @@
     <font>
       <sz val="12"/>
       <color rgb="FF212529"/>
-      <name val="微軟正黑體"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Microsoft JhengHei"/>
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
@@ -817,7 +838,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -864,6 +885,18 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -927,12 +960,12 @@
     </a:clrScheme>
     <a:fontScheme name="自訂 3">
       <a:majorFont>
-        <a:latin typeface="Arial"/>
+        <a:latin typeface="Microsoft JhengHei"/>
         <a:ea typeface="微軟正黑體"/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial"/>
+        <a:latin typeface="Microsoft JhengHei"/>
         <a:ea typeface="微軟正黑體"/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -1111,21 +1144,21 @@
     <tabColor theme="4" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:G23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="57.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.28515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.28515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="45.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="123.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.85546875" style="6"/>
+    <col min="1" max="1" width="3.5546875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="57.6640625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="28.44140625" style="6" customWidth="1"/>
+    <col min="4" max="4" width="35.33203125" style="6" customWidth="1"/>
+    <col min="5" max="5" width="22.33203125" style="6" customWidth="1"/>
+    <col min="6" max="6" width="45.5546875" style="6" customWidth="1"/>
+    <col min="7" max="7" width="123.6640625" style="6" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1">
+    <row r="1" spans="1:7" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1143,15 +1176,15 @@
         <v>3</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="38">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>1</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>5</v>
@@ -1169,58 +1202,58 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="38">
+    <row r="3" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="F3" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="E3" s="7" t="s">
+      <c r="G3" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="F3" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="38">
+    </row>
+    <row r="4" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="D4" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="E4" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="F4" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="G4" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="G4" s="8" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+    </row>
+    <row r="5" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>13</v>
@@ -1238,191 +1271,191 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="38">
+    <row r="6" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="E6" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="F6" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="G6" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="38">
+    </row>
+    <row r="7" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>6</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C7" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="F7" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="E7" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="F7" s="3" t="s">
+      <c r="G7" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="G7" s="8" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="38">
+    </row>
+    <row r="8" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G8" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="38">
+    </row>
+    <row r="9" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>8</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C9" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="E9" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="F9" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="G9" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="F9" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="57">
+    </row>
+    <row r="10" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="D10" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="E10" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="F10" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="G10" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="G10" s="8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="38">
+    </row>
+    <row r="11" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>10</v>
       </c>
       <c r="B11" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G11" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="38">
+    </row>
+    <row r="12" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="38">
+    </row>
+    <row r="13" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="E13" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" s="7" t="s">
+      <c r="F13" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E13" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="F13" s="6" t="s">
+      <c r="G13" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="G13" s="8" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="38">
+    </row>
+    <row r="14" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>13</v>
       </c>
@@ -1436,7 +1469,7 @@
         <v>18</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>17</v>
@@ -1445,211 +1478,211 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="38">
+    <row r="15" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>14</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>16</v>
       </c>
       <c r="D15" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E15" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="F15" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="G15" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="G15" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="57">
+    </row>
+    <row r="16" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C16" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F16" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="D16" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="F16" s="12" t="s">
+      <c r="G16" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="G16" s="8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="38">
+    </row>
+    <row r="17" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="D17" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="E17" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="G17" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="F17" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="38">
+    </row>
+    <row r="18" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G18" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C18" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="38">
+    </row>
+    <row r="19" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C19" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="D19" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="E19" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="G19" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="E19" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="19">
+    </row>
+    <row r="20" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>19</v>
       </c>
       <c r="B20" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="F20" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="C20" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="E20" s="7" t="s">
+      <c r="G20" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="F20" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="G20" s="8" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="38">
+    </row>
+    <row r="21" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>20</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C21" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D21" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="E21" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="F21" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="G21" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="F21" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+    </row>
+    <row r="22" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>21</v>
       </c>
       <c r="B22" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C22" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="D22" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="E22" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="F22" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="G22" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="F22" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="38">
+    </row>
+    <row r="23" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C23" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="D23" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="E23" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="F23" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="G23" s="8" t="s">
         <v>117</v>
-      </c>
-      <c r="G23" s="8" t="s">
-        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -1688,21 +1721,21 @@
     <tabColor theme="4"/>
   </sheetPr>
   <dimension ref="A1:G22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.140625" style="6" customWidth="1"/>
-    <col min="4" max="4" width="33.28515625" style="6" customWidth="1"/>
-    <col min="5" max="5" width="22.7109375" style="6" customWidth="1"/>
-    <col min="6" max="6" width="43.85546875" style="6" customWidth="1"/>
-    <col min="7" max="7" width="42.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.85546875" style="6"/>
+    <col min="1" max="1" width="2.77734375" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.88671875" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.6640625" style="6" customWidth="1"/>
+    <col min="6" max="6" width="42.77734375" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="52" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1">
+    <row r="1" spans="1:7" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1720,64 +1753,64 @@
         <v>3</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="38">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>141</v>
+      <c r="B2" s="17" t="s">
+        <v>140</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="D2" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="E2" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="G2" s="8" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="38">
+    </row>
+    <row r="3" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="D3" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>139</v>
-      </c>
       <c r="F3" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="38">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>144</v>
+        <v>152</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>154</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>145</v>
@@ -1785,46 +1818,60 @@
       <c r="E4" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="6" t="s">
         <v>147</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="38">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>153</v>
+      <c r="B5" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>23</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>5</v>
       </c>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="8"/>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="B6" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -1833,7 +1880,7 @@
       <c r="F7" s="4"/>
       <c r="G7" s="8"/>
     </row>
-    <row r="8" spans="1:7" ht="15.75">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -1842,7 +1889,7 @@
       <c r="F8" s="11"/>
       <c r="G8" s="8"/>
     </row>
-    <row r="9" spans="1:7" ht="15.75">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -1851,7 +1898,7 @@
       <c r="F9" s="11"/>
       <c r="G9" s="8"/>
     </row>
-    <row r="10" spans="1:7" ht="15.75">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>9</v>
       </c>
@@ -1859,7 +1906,7 @@
       <c r="E10" s="7"/>
       <c r="G10" s="8"/>
     </row>
-    <row r="11" spans="1:7" ht="15.75">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -1868,59 +1915,59 @@
       <c r="F11" s="3"/>
       <c r="G11" s="8"/>
     </row>
-    <row r="12" spans="1:7" ht="15.75">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="G12" s="8"/>
     </row>
-    <row r="13" spans="1:7" ht="15.75">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="G13" s="8"/>
     </row>
-    <row r="14" spans="1:7" ht="15.75">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="3"/>
       <c r="G14" s="8"/>
     </row>
-    <row r="15" spans="1:7" ht="15.75">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="12"/>
       <c r="G15" s="8"/>
     </row>
-    <row r="16" spans="1:7" ht="15.75">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
       <c r="F16" s="3"/>
       <c r="G16" s="8"/>
     </row>
-    <row r="17" spans="4:7" ht="15.75">
+    <row r="17" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
       <c r="G17" s="8"/>
     </row>
-    <row r="18" spans="4:7" ht="15.75">
+    <row r="18" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
       <c r="G18" s="8"/>
     </row>
-    <row r="19" spans="4:7" ht="15.75">
+    <row r="19" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
       <c r="G19" s="8"/>
     </row>
-    <row r="20" spans="4:7" ht="15.75">
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
       <c r="G20" s="8"/>
     </row>
-    <row r="21" spans="4:7" ht="15.75">
+    <row r="21" spans="4:7" x14ac:dyDescent="0.25">
       <c r="G21" s="8"/>
     </row>
-    <row r="22" spans="4:7" ht="15.75">
+    <row r="22" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
       <c r="G22" s="8"/>
@@ -1930,9 +1977,12 @@
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" xr:uid="{158A5F4F-C97E-4089-BA50-5616D4DCBAA0}"/>
     <hyperlink ref="G3" r:id="rId2" xr:uid="{DAF3C5B5-44BA-49AD-BA99-9161CE381FE1}"/>
+    <hyperlink ref="G6" r:id="rId3" xr:uid="{A143AFB3-8A14-4C9E-BBDF-4382164F17B0}"/>
+    <hyperlink ref="G4" r:id="rId4" xr:uid="{D05275B6-E52E-4EF6-8D12-5044F28A05C2}"/>
+    <hyperlink ref="G5" r:id="rId5" xr:uid="{48C0A51C-961F-4E15-A1C3-4884853F2424}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
 </worksheet>
 </file>
 
@@ -1942,21 +1992,21 @@
     <tabColor theme="4"/>
   </sheetPr>
   <dimension ref="A1:G22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="57.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.28515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.28515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="45.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="123.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.85546875" style="6"/>
+    <col min="1" max="1" width="3.5546875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="57.6640625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="28.44140625" style="6" customWidth="1"/>
+    <col min="4" max="4" width="35.33203125" style="6" customWidth="1"/>
+    <col min="5" max="5" width="22.33203125" style="6" customWidth="1"/>
+    <col min="6" max="6" width="45.5546875" style="6" customWidth="1"/>
+    <col min="7" max="7" width="123.6640625" style="6" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1">
+    <row r="1" spans="1:7" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1974,15 +2024,15 @@
         <v>3</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D2" s="7"/>
       <c r="E2" s="7"/>
@@ -1991,7 +2041,7 @@
       </c>
       <c r="G2" s="8"/>
     </row>
-    <row r="3" spans="1:7" ht="15.75">
+    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -2000,7 +2050,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="8"/>
     </row>
-    <row r="4" spans="1:7" ht="15.75">
+    <row r="4" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -2008,7 +2058,7 @@
       <c r="F4" s="10"/>
       <c r="G4" s="8"/>
     </row>
-    <row r="5" spans="1:7" ht="15.75">
+    <row r="5" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -2016,7 +2066,7 @@
       <c r="E5" s="7"/>
       <c r="G5" s="8"/>
     </row>
-    <row r="6" spans="1:7" ht="15.75">
+    <row r="6" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -2025,7 +2075,7 @@
       <c r="F6" s="3"/>
       <c r="G6" s="8"/>
     </row>
-    <row r="7" spans="1:7" ht="15.75">
+    <row r="7" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -2034,7 +2084,7 @@
       <c r="F7" s="4"/>
       <c r="G7" s="8"/>
     </row>
-    <row r="8" spans="1:7" ht="15.75">
+    <row r="8" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -2043,7 +2093,7 @@
       <c r="F8" s="11"/>
       <c r="G8" s="8"/>
     </row>
-    <row r="9" spans="1:7" ht="15.75">
+    <row r="9" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -2052,7 +2102,7 @@
       <c r="F9" s="11"/>
       <c r="G9" s="8"/>
     </row>
-    <row r="10" spans="1:7" ht="15.75">
+    <row r="10" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>9</v>
       </c>
@@ -2060,7 +2110,7 @@
       <c r="E10" s="7"/>
       <c r="G10" s="8"/>
     </row>
-    <row r="11" spans="1:7" ht="15.75">
+    <row r="11" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -2069,59 +2119,59 @@
       <c r="F11" s="3"/>
       <c r="G11" s="8"/>
     </row>
-    <row r="12" spans="1:7" ht="15.75">
+    <row r="12" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="G12" s="8"/>
     </row>
-    <row r="13" spans="1:7" ht="15.75">
+    <row r="13" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="G13" s="8"/>
     </row>
-    <row r="14" spans="1:7" ht="15.75">
+    <row r="14" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="3"/>
       <c r="G14" s="8"/>
     </row>
-    <row r="15" spans="1:7" ht="15.75">
+    <row r="15" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="12"/>
       <c r="G15" s="8"/>
     </row>
-    <row r="16" spans="1:7" ht="15.75">
+    <row r="16" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
       <c r="F16" s="3"/>
       <c r="G16" s="8"/>
     </row>
-    <row r="17" spans="4:7" ht="15.75">
+    <row r="17" spans="4:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
       <c r="G17" s="8"/>
     </row>
-    <row r="18" spans="4:7" ht="15.75">
+    <row r="18" spans="4:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
       <c r="G18" s="8"/>
     </row>
-    <row r="19" spans="4:7" ht="15.75">
+    <row r="19" spans="4:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
       <c r="G19" s="8"/>
     </row>
-    <row r="20" spans="4:7" ht="15.75">
+    <row r="20" spans="4:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
       <c r="G20" s="8"/>
     </row>
-    <row r="21" spans="4:7" ht="15.75">
+    <row r="21" spans="4:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="G21" s="8"/>
     </row>
-    <row r="22" spans="4:7" ht="15.75">
+    <row r="22" spans="4:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
       <c r="G22" s="8"/>

--- a/competition/專題競賽資訊.xlsx
+++ b/competition/專題競賽資訊.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\benj1\Documents\SaveMyBook\competition\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF3AE21B-44D0-4161-9E93-FDC23F939508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97E0B90C-0775-4D5E-A45D-C7D07B4492F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{285F9FD4-B296-469E-ADA7-FB304A9A05A2}"/>
   </bookViews>
@@ -633,13 +633,6 @@
     <t>2026第31屆大專校院資訊應用服務創新競賽</t>
   </si>
   <si>
-    <t>2026/8/1(五)~2026/9/30(二)</t>
-  </si>
-  <si>
-    <t>初賽：書面審查
-決賽：國立臺灣大學</t>
-  </si>
-  <si>
     <t>初賽：2026/10/13(二)~2026/10/23(五)
 決賽：2026/11/7(六)</t>
   </si>
@@ -719,6 +712,13 @@
   <si>
     <t>初賽：書面審查
 決賽：國立高雄科技大學</t>
+  </si>
+  <si>
+    <t>2026/8/3(一)~2026/10/5(一)</t>
+  </si>
+  <si>
+    <t>初賽：書面審查
+決賽：國立臺灣大學綜合體育館</t>
   </si>
 </sst>
 </file>
@@ -838,7 +838,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -887,16 +887,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1144,7 +1135,7 @@
     <tabColor theme="4" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.5546875" style="5" customWidth="1"/>
     <col min="2" max="2" width="57.6640625" style="6" customWidth="1"/>
@@ -1248,7 +1239,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -1414,7 +1405,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>21</v>
@@ -1593,7 +1584,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>19</v>
       </c>
@@ -1621,7 +1612,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>107</v>
@@ -1639,7 +1630,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>21</v>
       </c>
@@ -1723,11 +1714,11 @@
   <dimension ref="A1:G22"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.77734375" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3" style="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="36.109375" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26.88671875" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="33.109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.6640625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="25.88671875" style="6" customWidth="1"/>
     <col min="6" max="6" width="42.77734375" style="6" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="52" style="6" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="8.88671875" style="6"/>
@@ -1760,11 +1751,11 @@
       <c r="A2" s="5">
         <v>1</v>
       </c>
-      <c r="B2" s="17" t="s">
-        <v>140</v>
+      <c r="B2" s="16" t="s">
+        <v>138</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>132</v>
@@ -1779,7 +1770,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -1787,13 +1778,13 @@
         <v>136</v>
       </c>
       <c r="C3" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="D3" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="D3" s="7" t="s">
-        <v>139</v>
-      </c>
       <c r="E3" s="7" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="F3" s="11" t="s">
         <v>86</v>
@@ -1807,22 +1798,22 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C4" s="15" t="s">
         <v>152</v>
       </c>
-      <c r="C4" s="15" t="s">
-        <v>154</v>
-      </c>
       <c r="D4" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="F4" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="E4" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>147</v>
-      </c>
       <c r="G4" s="8" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
@@ -1830,22 +1821,22 @@
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="E5" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="8" t="s">
         <v>157</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="E5" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="F5" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
@@ -1853,22 +1844,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="F6" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>151</v>
-      </c>
       <c r="G6" s="8" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -1992,7 +1983,7 @@
     <tabColor theme="4"/>
   </sheetPr>
   <dimension ref="A1:G22"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.5546875" style="5" customWidth="1"/>
     <col min="2" max="2" width="57.6640625" style="6" customWidth="1"/>
@@ -2027,7 +2018,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -2041,7 +2032,7 @@
       </c>
       <c r="G2" s="8"/>
     </row>
-    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -2050,7 +2041,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="8"/>
     </row>
-    <row r="4" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -2058,7 +2049,7 @@
       <c r="F4" s="10"/>
       <c r="G4" s="8"/>
     </row>
-    <row r="5" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -2066,7 +2057,7 @@
       <c r="E5" s="7"/>
       <c r="G5" s="8"/>
     </row>
-    <row r="6" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -2075,7 +2066,7 @@
       <c r="F6" s="3"/>
       <c r="G6" s="8"/>
     </row>
-    <row r="7" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -2084,7 +2075,7 @@
       <c r="F7" s="4"/>
       <c r="G7" s="8"/>
     </row>
-    <row r="8" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -2093,7 +2084,7 @@
       <c r="F8" s="11"/>
       <c r="G8" s="8"/>
     </row>
-    <row r="9" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -2102,7 +2093,7 @@
       <c r="F9" s="11"/>
       <c r="G9" s="8"/>
     </row>
-    <row r="10" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>9</v>
       </c>
@@ -2110,7 +2101,7 @@
       <c r="E10" s="7"/>
       <c r="G10" s="8"/>
     </row>
-    <row r="11" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -2119,59 +2110,59 @@
       <c r="F11" s="3"/>
       <c r="G11" s="8"/>
     </row>
-    <row r="12" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="G12" s="8"/>
     </row>
-    <row r="13" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="G13" s="8"/>
     </row>
-    <row r="14" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="3"/>
       <c r="G14" s="8"/>
     </row>
-    <row r="15" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="12"/>
       <c r="G15" s="8"/>
     </row>
-    <row r="16" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
       <c r="F16" s="3"/>
       <c r="G16" s="8"/>
     </row>
-    <row r="17" spans="4:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
       <c r="G17" s="8"/>
     </row>
-    <row r="18" spans="4:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
       <c r="G18" s="8"/>
     </row>
-    <row r="19" spans="4:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
       <c r="G19" s="8"/>
     </row>
-    <row r="20" spans="4:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
       <c r="G20" s="8"/>
     </row>
-    <row r="21" spans="4:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="4:7" x14ac:dyDescent="0.25">
       <c r="G21" s="8"/>
     </row>
-    <row r="22" spans="4:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
       <c r="G22" s="8"/>

--- a/competition/專題競賽資訊.xlsx
+++ b/competition/專題競賽資訊.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\benj1\Documents\SaveMyBook\competition\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\OneDrive\文件\SaveMyBook\competition\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97E0B90C-0775-4D5E-A45D-C7D07B4492F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9948B836-213F-430F-8F18-03D12F12E6B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{285F9FD4-B296-469E-ADA7-FB304A9A05A2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{285F9FD4-B296-469E-ADA7-FB304A9A05A2}"/>
   </bookViews>
   <sheets>
     <sheet name="2025年相關競賽" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="167">
   <si>
     <t>競賽名稱</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -421,7 +421,7 @@
       <rPr>
         <sz val="12"/>
         <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
+        <rFont val="微軟正黑體"/>
         <family val="2"/>
         <charset val="136"/>
         <scheme val="minor"/>
@@ -437,7 +437,7 @@
       <rPr>
         <sz val="12"/>
         <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
+        <rFont val="微軟正黑體"/>
         <family val="2"/>
         <charset val="136"/>
         <scheme val="minor"/>
@@ -691,20 +691,10 @@
     <t>2026/9/1(二)~2026/12/1(二)</t>
   </si>
   <si>
-    <t>2026/9/1(二)~2026/10/22(四）</t>
-  </si>
-  <si>
     <t>2025第六屆高科盃全國商業智慧競賽</t>
   </si>
   <si>
     <t>第七屆高科盃全國商業智慧競賽</t>
-  </si>
-  <si>
-    <t>~2026/10/28(三）</t>
-  </si>
-  <si>
-    <t>初賽：2026/10/28(三）
-決賽：2026/11/22(日)</t>
   </si>
   <si>
     <t>https://ic.dxing888.com/</t>
@@ -719,6 +709,43 @@
   <si>
     <t>初賽：書面審查
 決賽：國立臺灣大學綜合體育館</t>
+  </si>
+  <si>
+    <t>2026年 iLink 生成式AI創意應用大賽</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026/9/7(一)~2026/10/19(一)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ilink.usc.edu.tw/?Lang=zh-tw</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>初賽：2026/10/28(三)
+決賽：2026/11/22(日)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026/9/1(二)~2026/10/22(四)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>~2026/10/28(三)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>決賽：2026/12/5(六)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>實踐大學、iLink 人文社會與產業實務創新鏈結總計畫辦公室</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>決賽：實踐大學臺北校區</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -729,7 +756,7 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Microsoft JhengHei"/>
+      <name val="微軟正黑體"/>
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
@@ -738,14 +765,14 @@
       <b/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Microsoft JhengHei"/>
+      <name val="微軟正黑體"/>
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="Microsoft JhengHei"/>
+      <name val="微軟正黑體"/>
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
@@ -754,7 +781,7 @@
       <u/>
       <sz val="12"/>
       <color theme="10"/>
-      <name val="Microsoft JhengHei"/>
+      <name val="微軟正黑體"/>
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
@@ -762,7 +789,7 @@
     <font>
       <sz val="12"/>
       <color rgb="FF333333"/>
-      <name val="Microsoft JhengHei"/>
+      <name val="微軟正黑體"/>
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
@@ -770,7 +797,7 @@
     <font>
       <sz val="12"/>
       <color rgb="FF18212B"/>
-      <name val="Microsoft JhengHei"/>
+      <name val="微軟正黑體"/>
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
@@ -778,7 +805,7 @@
     <font>
       <sz val="12"/>
       <color rgb="FF212121"/>
-      <name val="Microsoft JhengHei"/>
+      <name val="微軟正黑體"/>
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
@@ -786,7 +813,7 @@
     <font>
       <sz val="12"/>
       <color rgb="FF212529"/>
-      <name val="Microsoft JhengHei"/>
+      <name val="微軟正黑體"/>
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
@@ -795,7 +822,7 @@
       <strike/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Microsoft JhengHei"/>
+      <name val="微軟正黑體"/>
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
@@ -1135,19 +1162,19 @@
     <tabColor theme="4" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.9140625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.5546875" style="5" customWidth="1"/>
+    <col min="1" max="1" width="3.58203125" style="5" customWidth="1"/>
     <col min="2" max="2" width="57.6640625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="28.44140625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="28.4140625" style="6" customWidth="1"/>
     <col min="4" max="4" width="35.33203125" style="6" customWidth="1"/>
     <col min="5" max="5" width="22.33203125" style="6" customWidth="1"/>
-    <col min="6" max="6" width="45.5546875" style="6" customWidth="1"/>
+    <col min="6" max="6" width="45.58203125" style="6" customWidth="1"/>
     <col min="7" max="7" width="123.6640625" style="6" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="6"/>
+    <col min="8" max="16384" width="8.9140625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>68</v>
       </c>
@@ -1170,7 +1197,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -1193,7 +1220,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -1216,7 +1243,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -1239,7 +1266,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -1262,7 +1289,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -1285,7 +1312,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -1308,7 +1335,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -1331,7 +1358,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -1354,7 +1381,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>9</v>
       </c>
@@ -1377,7 +1404,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -1400,12 +1427,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>21</v>
@@ -1423,7 +1450,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>12</v>
       </c>
@@ -1446,7 +1473,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>13</v>
       </c>
@@ -1469,7 +1496,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>14</v>
       </c>
@@ -1492,7 +1519,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
         <v>15</v>
       </c>
@@ -1515,7 +1542,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>16</v>
       </c>
@@ -1538,7 +1565,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
         <v>17</v>
       </c>
@@ -1561,7 +1588,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>18</v>
       </c>
@@ -1584,7 +1611,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="5">
         <v>19</v>
       </c>
@@ -1607,7 +1634,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>20</v>
       </c>
@@ -1630,7 +1657,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="5">
         <v>21</v>
       </c>
@@ -1653,7 +1680,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>22</v>
       </c>
@@ -1711,20 +1738,20 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G23"/>
+  <sheetFormatPr defaultColWidth="8.9140625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.88671875" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="33.109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.88671875" style="6" customWidth="1"/>
-    <col min="6" max="6" width="42.77734375" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.08203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.9140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.08203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.9140625" style="6" customWidth="1"/>
+    <col min="6" max="6" width="42.75" style="6" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="52" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="6"/>
+    <col min="8" max="16384" width="8.9140625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>68</v>
       </c>
@@ -1747,7 +1774,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -1770,7 +1797,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -1778,13 +1805,13 @@
         <v>136</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>137</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F3" s="11" t="s">
         <v>86</v>
@@ -1793,94 +1820,108 @@
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>145</v>
+        <v>166</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>165</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>154</v>
+      <c r="B5" s="6" t="s">
+        <v>150</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>23</v>
+        <v>145</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>151</v>
+      <c r="B6" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>163</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>149</v>
+        <v>155</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="8"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>7</v>
       </c>
       <c r="D8" s="7"/>
       <c r="E8" s="7"/>
-      <c r="F8" s="11"/>
+      <c r="F8" s="4"/>
       <c r="G8" s="8"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -1889,91 +1930,101 @@
       <c r="F9" s="11"/>
       <c r="G9" s="8"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>9</v>
       </c>
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
+      <c r="F10" s="11"/>
       <c r="G10" s="8"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>10</v>
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
-      <c r="F11" s="3"/>
       <c r="G11" s="8"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="5">
+        <v>11</v>
+      </c>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
+      <c r="F12" s="3"/>
       <c r="G12" s="8"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="G13" s="8"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
-      <c r="F14" s="3"/>
       <c r="G14" s="8"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
-      <c r="F15" s="12"/>
+      <c r="F15" s="3"/>
       <c r="G15" s="8"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
-      <c r="F16" s="3"/>
+      <c r="F16" s="12"/>
       <c r="G16" s="8"/>
     </row>
-    <row r="17" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
+      <c r="F17" s="3"/>
       <c r="G17" s="8"/>
     </row>
-    <row r="18" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
       <c r="G18" s="8"/>
     </row>
-    <row r="19" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
       <c r="G19" s="8"/>
     </row>
-    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
       <c r="G20" s="8"/>
     </row>
-    <row r="21" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
       <c r="G21" s="8"/>
     </row>
-    <row r="22" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
+    <row r="22" spans="4:7" x14ac:dyDescent="0.3">
       <c r="G22" s="8"/>
+    </row>
+    <row r="23" spans="4:7" x14ac:dyDescent="0.3">
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="G23" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" xr:uid="{158A5F4F-C97E-4089-BA50-5616D4DCBAA0}"/>
     <hyperlink ref="G3" r:id="rId2" xr:uid="{DAF3C5B5-44BA-49AD-BA99-9161CE381FE1}"/>
-    <hyperlink ref="G6" r:id="rId3" xr:uid="{A143AFB3-8A14-4C9E-BBDF-4382164F17B0}"/>
-    <hyperlink ref="G4" r:id="rId4" xr:uid="{D05275B6-E52E-4EF6-8D12-5044F28A05C2}"/>
-    <hyperlink ref="G5" r:id="rId5" xr:uid="{48C0A51C-961F-4E15-A1C3-4884853F2424}"/>
+    <hyperlink ref="G7" r:id="rId3" xr:uid="{A143AFB3-8A14-4C9E-BBDF-4382164F17B0}"/>
+    <hyperlink ref="G5" r:id="rId4" xr:uid="{D05275B6-E52E-4EF6-8D12-5044F28A05C2}"/>
+    <hyperlink ref="G6" r:id="rId5" xr:uid="{48C0A51C-961F-4E15-A1C3-4884853F2424}"/>
+    <hyperlink ref="G4" r:id="rId6" xr:uid="{BDECB891-6800-4312-BD52-462C4CF8E819}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId7"/>
 </worksheet>
 </file>
 
@@ -1983,19 +2034,19 @@
     <tabColor theme="4"/>
   </sheetPr>
   <dimension ref="A1:G22"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.9140625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.5546875" style="5" customWidth="1"/>
+    <col min="1" max="1" width="3.58203125" style="5" customWidth="1"/>
     <col min="2" max="2" width="57.6640625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="28.44140625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="28.4140625" style="6" customWidth="1"/>
     <col min="4" max="4" width="35.33203125" style="6" customWidth="1"/>
     <col min="5" max="5" width="22.33203125" style="6" customWidth="1"/>
-    <col min="6" max="6" width="45.5546875" style="6" customWidth="1"/>
+    <col min="6" max="6" width="45.58203125" style="6" customWidth="1"/>
     <col min="7" max="7" width="123.6640625" style="6" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="6"/>
+    <col min="8" max="16384" width="8.9140625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>68</v>
       </c>
@@ -2018,7 +2069,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -2032,7 +2083,7 @@
       </c>
       <c r="G2" s="8"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -2041,7 +2092,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="8"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -2049,7 +2100,7 @@
       <c r="F4" s="10"/>
       <c r="G4" s="8"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -2057,7 +2108,7 @@
       <c r="E5" s="7"/>
       <c r="G5" s="8"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -2066,7 +2117,7 @@
       <c r="F6" s="3"/>
       <c r="G6" s="8"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -2075,7 +2126,7 @@
       <c r="F7" s="4"/>
       <c r="G7" s="8"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -2084,7 +2135,7 @@
       <c r="F8" s="11"/>
       <c r="G8" s="8"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -2093,7 +2144,7 @@
       <c r="F9" s="11"/>
       <c r="G9" s="8"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>9</v>
       </c>
@@ -2101,7 +2152,7 @@
       <c r="E10" s="7"/>
       <c r="G10" s="8"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -2110,59 +2161,59 @@
       <c r="F11" s="3"/>
       <c r="G11" s="8"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="G12" s="8"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="G13" s="8"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="3"/>
       <c r="G14" s="8"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="12"/>
       <c r="G15" s="8"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
       <c r="F16" s="3"/>
       <c r="G16" s="8"/>
     </row>
-    <row r="17" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
       <c r="G17" s="8"/>
     </row>
-    <row r="18" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
       <c r="G18" s="8"/>
     </row>
-    <row r="19" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
       <c r="G19" s="8"/>
     </row>
-    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
       <c r="G20" s="8"/>
     </row>
-    <row r="21" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="4:7" x14ac:dyDescent="0.3">
       <c r="G21" s="8"/>
     </row>
-    <row r="22" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
       <c r="G22" s="8"/>

--- a/competition/專題競賽資訊.xlsx
+++ b/competition/專題競賽資訊.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\OneDrive\文件\SaveMyBook\competition\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9948B836-213F-430F-8F18-03D12F12E6B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89265B61-BFA3-48D4-880E-50353DA2DA33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{285F9FD4-B296-469E-ADA7-FB304A9A05A2}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="161">
   <si>
     <t>競賽名稱</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -711,18 +711,6 @@
 決賽：國立臺灣大學綜合體育館</t>
   </si>
   <si>
-    <t>2026年 iLink 生成式AI創意應用大賽</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026/9/7(一)~2026/10/19(一)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://ilink.usc.edu.tw/?Lang=zh-tw</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>初賽：2026/10/28(三)
 決賽：2026/11/22(日)</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -733,18 +721,6 @@
   </si>
   <si>
     <t>~2026/10/28(三)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>決賽：2026/12/5(六)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>實踐大學、iLink 人文社會與產業實務創新鏈結總計畫辦公室</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>決賽：實踐大學臺北校區</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1825,91 +1801,73 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="C4" s="15" t="s">
         <v>159</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>165</v>
+        <v>144</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>150</v>
+      <c r="B5" s="7" t="s">
+        <v>153</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>145</v>
+        <v>23</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>163</v>
+      <c r="B6" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>151</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>161</v>
+        <v>140</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>23</v>
+        <v>141</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>149</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="46.8" x14ac:dyDescent="0.3">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>6</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -2018,13 +1976,12 @@
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" xr:uid="{158A5F4F-C97E-4089-BA50-5616D4DCBAA0}"/>
     <hyperlink ref="G3" r:id="rId2" xr:uid="{DAF3C5B5-44BA-49AD-BA99-9161CE381FE1}"/>
-    <hyperlink ref="G7" r:id="rId3" xr:uid="{A143AFB3-8A14-4C9E-BBDF-4382164F17B0}"/>
-    <hyperlink ref="G5" r:id="rId4" xr:uid="{D05275B6-E52E-4EF6-8D12-5044F28A05C2}"/>
-    <hyperlink ref="G6" r:id="rId5" xr:uid="{48C0A51C-961F-4E15-A1C3-4884853F2424}"/>
-    <hyperlink ref="G4" r:id="rId6" xr:uid="{BDECB891-6800-4312-BD52-462C4CF8E819}"/>
+    <hyperlink ref="G6" r:id="rId3" xr:uid="{A143AFB3-8A14-4C9E-BBDF-4382164F17B0}"/>
+    <hyperlink ref="G4" r:id="rId4" xr:uid="{D05275B6-E52E-4EF6-8D12-5044F28A05C2}"/>
+    <hyperlink ref="G5" r:id="rId5" xr:uid="{48C0A51C-961F-4E15-A1C3-4884853F2424}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId7"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
 </worksheet>
 </file>
 

--- a/competition/專題競賽資訊.xlsx
+++ b/competition/專題競賽資訊.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\OneDrive\文件\SaveMyBook\competition\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Xuan\SaveMyBook\competition\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89265B61-BFA3-48D4-880E-50353DA2DA33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C27E4DD5-14DB-4056-9A0F-EC4ECF752994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{285F9FD4-B296-469E-ADA7-FB304A9A05A2}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{285F9FD4-B296-469E-ADA7-FB304A9A05A2}"/>
   </bookViews>
   <sheets>
     <sheet name="2025年相關競賽" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="184">
   <si>
     <t>競賽名稱</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -633,94 +633,191 @@
     <t>2026第31屆大專校院資訊應用服務創新競賽</t>
   </si>
   <si>
+    <t>萬潤2026創新創意競賽</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025全國AI專題創意競賽</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>初賽：2026/12/11(五)
+決賽：2026/12/19(六)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>初賽：書面審查
+決賽：國立臺南大學中山館</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://eedept.ncue.edu.tw/innovation2026/index.html</t>
+  </si>
+  <si>
+    <t>初賽：2026/11/12(四)
+決賽：2026/11/19(四)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>初賽：書面審查
+決賽：國立彰化師大工學院</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>國立彰化師範大學工學院、彰化縣產學精進協會</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>~2026/8/31(一)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026全國AI專題創意競賽</t>
+  </si>
+  <si>
+    <t>https://phpweb4.nutn.edu.tw/ilt/wordpress/?page_id=4308</t>
+  </si>
+  <si>
+    <t>2026全國大專院校產學創新實作競賽</t>
+  </si>
+  <si>
+    <t>2026/9/1(二)~2026/12/1(二)</t>
+  </si>
+  <si>
+    <t>2025第六屆高科盃全國商業智慧競賽</t>
+  </si>
+  <si>
+    <t>第七屆高科盃全國商業智慧競賽</t>
+  </si>
+  <si>
+    <t>https://ic.dxing888.com/</t>
+  </si>
+  <si>
+    <t>初賽：書面審查
+決賽：國立高雄科技大學</t>
+  </si>
+  <si>
+    <t>2026/8/3(一)~2026/10/5(一)</t>
+  </si>
+  <si>
+    <t>初賽：書面審查
+決賽：國立臺灣大學綜合體育館</t>
+  </si>
+  <si>
+    <t>初賽：2026/10/28(三)
+決賽：2026/11/22(日)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026/9/1(二)~2026/10/22(四)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>~2026/10/28(三)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>~2026/12/04(五)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>初賽：書面審查
+分組決賽/總決賽：龍華科技大學</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>龍華科技大學資訊管理系</t>
+  </si>
+  <si>
+    <t>初賽：2026/12/11(五)
+決賽：2026/12/17(四)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026全國資訊管理前瞻技術研討會暨專題競賽(AMITAC 2025)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026智慧永續循環技術研討會暨專題競賽</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>~2026/11/22(日)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>初賽：2026/11/27(五)
+決賽：2026/12/12(六)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>初賽：書面審查
+分組決賽/總決賽：東海大學人文大樓</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026年生成式人工智慧創新應用國際競賽</t>
+  </si>
+  <si>
+    <t>~2026/11/25(三)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>初賽：2026/11/25(三)
+決賽：2026/12/18(五)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>長榮大學管理學院</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>初賽：書面審查
+線上頒獎典禮</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://dweb.cjcu.edu.tw/com/spotlight/8394</t>
+  </si>
+  <si>
+    <t>https://3goodai.fgu.edu.tw/</t>
+  </si>
+  <si>
+    <t>初賽：書面審查
+成果展示暨頒獎典禮：佛光大學雲五館一樓藍海區</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>初賽：2026/10/13(二)~2026/10/23(五)
 決賽：2026/11/7(六)</t>
-  </si>
-  <si>
-    <t>萬潤2026創新創意競賽</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025全國AI專題創意競賽</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>初賽：2026/12/11(五)
-決賽：2026/12/19(六)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>初賽：書面審查
-決賽：國立臺南大學中山館</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://eedept.ncue.edu.tw/innovation2026/index.html</t>
-  </si>
-  <si>
-    <t>初賽：2026/11/12(四)
-決賽：2026/11/19(四)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>初賽：書面審查
-決賽：國立彰化師大工學院</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>國立彰化師範大學工學院、彰化縣產學精進協會</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>~2026/8/31(一)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026全國AI專題創意競賽</t>
-  </si>
-  <si>
-    <t>https://phpweb4.nutn.edu.tw/ilt/wordpress/?page_id=4308</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>初賽：2026/12/01(二)~115/12/15(二)
+決賽：2026/12/18(五)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>佛光大學</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>國立臺南大學理工學院、數位學習科技學系、電機工程學系、知識應用暨網路服務研究中心、AI 智慧技術與應用人才培訓據點</t>
-  </si>
-  <si>
-    <t>2026全國大專院校產學創新實作競賽</t>
-  </si>
-  <si>
-    <t>2026/9/1(二)~2026/12/1(二)</t>
-  </si>
-  <si>
-    <t>2025第六屆高科盃全國商業智慧競賽</t>
-  </si>
-  <si>
-    <t>第七屆高科盃全國商業智慧競賽</t>
-  </si>
-  <si>
-    <t>https://ic.dxing888.com/</t>
-  </si>
-  <si>
-    <t>初賽：書面審查
-決賽：國立高雄科技大學</t>
-  </si>
-  <si>
-    <t>2026/8/3(一)~2026/10/5(一)</t>
-  </si>
-  <si>
-    <t>初賽：書面審查
-決賽：國立臺灣大學綜合體育館</t>
-  </si>
-  <si>
-    <t>初賽：2026/10/28(三)
-決賽：2026/11/22(日)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026/9/1(二)~2026/10/22(四)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>~2026/10/28(三)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>東海大學</t>
+  </si>
+  <si>
+    <t>https://im.lhu.edu.tw/p/405-1010-26806,c1211.php?Lang=zh-tw</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026/10/01(四)~2026/11/30(一)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://enger.thu.edu.tw/info-on-home-page/2026%e6%99%ba%e6%85%a7%e6%b0%b8%e7%ba%8c%e5%be%aa%e7%92%b0%e6%8a%80%e8%a1%93%e7%a0%94%e8%a8%8e%e6%9c%83%e6%9a%a8%e5%b0%88%e9%a1%8c%e7%ab%b6%e8%b3%bd/</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -728,7 +825,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -803,6 +900,12 @@
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="13"/>
+      <color rgb="FF262626"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -841,7 +944,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -892,6 +995,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1138,19 +1244,19 @@
     <tabColor theme="4" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultColWidth="8.9140625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.92578125" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="3.58203125" style="5" customWidth="1"/>
-    <col min="2" max="2" width="57.6640625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="28.4140625" style="6" customWidth="1"/>
-    <col min="4" max="4" width="35.33203125" style="6" customWidth="1"/>
-    <col min="5" max="5" width="22.33203125" style="6" customWidth="1"/>
-    <col min="6" max="6" width="45.58203125" style="6" customWidth="1"/>
-    <col min="7" max="7" width="123.6640625" style="6" customWidth="1"/>
-    <col min="8" max="16384" width="8.9140625" style="6"/>
+    <col min="1" max="1" width="3.5703125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="57.640625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="28.42578125" style="6" customWidth="1"/>
+    <col min="4" max="4" width="35.35546875" style="6" customWidth="1"/>
+    <col min="5" max="5" width="22.35546875" style="6" customWidth="1"/>
+    <col min="6" max="6" width="45.5703125" style="6" customWidth="1"/>
+    <col min="7" max="7" width="123.640625" style="6" customWidth="1"/>
+    <col min="8" max="16384" width="8.92578125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>68</v>
       </c>
@@ -1173,7 +1279,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="31" x14ac:dyDescent="0.35">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -1196,7 +1302,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="31" x14ac:dyDescent="0.35">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -1219,7 +1325,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="31" x14ac:dyDescent="0.35">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -1242,7 +1348,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -1265,7 +1371,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="31" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -1288,7 +1394,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="31" x14ac:dyDescent="0.35">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -1311,7 +1417,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="31" x14ac:dyDescent="0.35">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -1334,7 +1440,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="31" x14ac:dyDescent="0.35">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -1357,7 +1463,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A10" s="5">
         <v>9</v>
       </c>
@@ -1380,7 +1486,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="31" x14ac:dyDescent="0.35">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -1403,12 +1509,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="31" x14ac:dyDescent="0.35">
       <c r="A12" s="5">
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>21</v>
@@ -1426,7 +1532,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="31" x14ac:dyDescent="0.35">
       <c r="A13" s="5">
         <v>12</v>
       </c>
@@ -1449,7 +1555,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="31" x14ac:dyDescent="0.35">
       <c r="A14" s="5">
         <v>13</v>
       </c>
@@ -1472,7 +1578,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="31" x14ac:dyDescent="0.35">
       <c r="A15" s="5">
         <v>14</v>
       </c>
@@ -1495,7 +1601,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A16" s="5">
         <v>15</v>
       </c>
@@ -1518,7 +1624,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="31" x14ac:dyDescent="0.35">
       <c r="A17" s="5">
         <v>16</v>
       </c>
@@ -1541,7 +1647,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="31" x14ac:dyDescent="0.35">
       <c r="A18" s="5">
         <v>17</v>
       </c>
@@ -1564,7 +1670,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="31" x14ac:dyDescent="0.35">
       <c r="A19" s="5">
         <v>18</v>
       </c>
@@ -1587,7 +1693,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="5">
         <v>19</v>
       </c>
@@ -1610,12 +1716,12 @@
         <v>106</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="31" x14ac:dyDescent="0.35">
       <c r="A21" s="5">
         <v>20</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>107</v>
@@ -1633,7 +1739,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="5">
         <v>21</v>
       </c>
@@ -1656,7 +1762,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="31" x14ac:dyDescent="0.35">
       <c r="A23" s="5">
         <v>22</v>
       </c>
@@ -1715,19 +1821,19 @@
     <tabColor theme="4"/>
   </sheetPr>
   <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultColWidth="8.9140625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.92578125" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.08203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.9140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="33.08203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.9140625" style="6" customWidth="1"/>
-    <col min="6" max="6" width="42.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.35546875" style="6" customWidth="1"/>
+    <col min="3" max="3" width="26.92578125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.0703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="38.0703125" style="6" customWidth="1"/>
+    <col min="6" max="6" width="42.7109375" style="6" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="52" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.9140625" style="6"/>
+    <col min="8" max="16384" width="8.92578125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>68</v>
       </c>
@@ -1750,15 +1856,15 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="31" x14ac:dyDescent="0.35">
       <c r="A2" s="5">
         <v>1</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>132</v>
@@ -1773,7 +1879,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="31" x14ac:dyDescent="0.35">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -1781,13 +1887,13 @@
         <v>136</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>137</v>
+        <v>176</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F3" s="11" t="s">
         <v>86</v>
@@ -1796,116 +1902,173 @@
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="31" x14ac:dyDescent="0.35">
       <c r="A4" s="5">
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D4" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="F4" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="F4" s="6" t="s">
-        <v>145</v>
-      </c>
       <c r="G4" s="8" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="31" x14ac:dyDescent="0.35">
       <c r="A5" s="5">
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>153</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>155</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>23</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="46.8" x14ac:dyDescent="0.3">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="31" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>140</v>
+        <v>166</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>149</v>
+        <v>167</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>180</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="31" x14ac:dyDescent="0.35">
       <c r="A7" s="5">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B7" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A8" s="5">
         <v>7</v>
       </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="8"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B8" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A9" s="5">
         <v>8</v>
       </c>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="8"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B9" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="31" x14ac:dyDescent="0.35">
       <c r="A10" s="5">
         <v>9</v>
       </c>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="8"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B10" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="F10" t="s">
+        <v>161</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="5">
         <v>10</v>
       </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="G11" s="8"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="5">
         <v>11</v>
       </c>
@@ -1914,59 +2077,59 @@
       <c r="F12" s="3"/>
       <c r="G12" s="8"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="G13" s="8"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="G14" s="8"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="3"/>
       <c r="G15" s="8"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
       <c r="F16" s="12"/>
       <c r="G16" s="8"/>
     </row>
-    <row r="17" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
       <c r="F17" s="3"/>
       <c r="G17" s="8"/>
     </row>
-    <row r="18" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
       <c r="G18" s="8"/>
     </row>
-    <row r="19" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
       <c r="G19" s="8"/>
     </row>
-    <row r="20" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
       <c r="G20" s="8"/>
     </row>
-    <row r="21" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
       <c r="F21" s="7"/>
       <c r="G21" s="8"/>
     </row>
-    <row r="22" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="4:7" x14ac:dyDescent="0.35">
       <c r="G22" s="8"/>
     </row>
-    <row r="23" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
       <c r="G23" s="8"/>
@@ -1976,12 +2139,14 @@
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" xr:uid="{158A5F4F-C97E-4089-BA50-5616D4DCBAA0}"/>
     <hyperlink ref="G3" r:id="rId2" xr:uid="{DAF3C5B5-44BA-49AD-BA99-9161CE381FE1}"/>
-    <hyperlink ref="G6" r:id="rId3" xr:uid="{A143AFB3-8A14-4C9E-BBDF-4382164F17B0}"/>
+    <hyperlink ref="G9" r:id="rId3" xr:uid="{A143AFB3-8A14-4C9E-BBDF-4382164F17B0}"/>
     <hyperlink ref="G4" r:id="rId4" xr:uid="{D05275B6-E52E-4EF6-8D12-5044F28A05C2}"/>
     <hyperlink ref="G5" r:id="rId5" xr:uid="{48C0A51C-961F-4E15-A1C3-4884853F2424}"/>
+    <hyperlink ref="G10" r:id="rId6" xr:uid="{8577FF30-EE87-46EC-A8B9-6588335C2AC6}"/>
+    <hyperlink ref="G6" r:id="rId7" xr:uid="{15128193-11BE-4EA7-A0D1-AAE7972DCD68}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId8"/>
 </worksheet>
 </file>
 
@@ -1991,19 +2156,19 @@
     <tabColor theme="4"/>
   </sheetPr>
   <dimension ref="A1:G22"/>
-  <sheetFormatPr defaultColWidth="8.9140625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.92578125" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="3.58203125" style="5" customWidth="1"/>
-    <col min="2" max="2" width="57.6640625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="28.4140625" style="6" customWidth="1"/>
-    <col min="4" max="4" width="35.33203125" style="6" customWidth="1"/>
-    <col min="5" max="5" width="22.33203125" style="6" customWidth="1"/>
-    <col min="6" max="6" width="45.58203125" style="6" customWidth="1"/>
-    <col min="7" max="7" width="123.6640625" style="6" customWidth="1"/>
-    <col min="8" max="16384" width="8.9140625" style="6"/>
+    <col min="1" max="1" width="3.5703125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="57.640625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="28.42578125" style="6" customWidth="1"/>
+    <col min="4" max="4" width="35.35546875" style="6" customWidth="1"/>
+    <col min="5" max="5" width="22.35546875" style="6" customWidth="1"/>
+    <col min="6" max="6" width="45.5703125" style="6" customWidth="1"/>
+    <col min="7" max="7" width="123.640625" style="6" customWidth="1"/>
+    <col min="8" max="16384" width="8.92578125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>68</v>
       </c>
@@ -2026,7 +2191,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -2040,7 +2205,7 @@
       </c>
       <c r="G2" s="8"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -2049,7 +2214,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="8"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -2057,7 +2222,7 @@
       <c r="F4" s="10"/>
       <c r="G4" s="8"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -2065,7 +2230,7 @@
       <c r="E5" s="7"/>
       <c r="G5" s="8"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -2074,7 +2239,7 @@
       <c r="F6" s="3"/>
       <c r="G6" s="8"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -2083,7 +2248,7 @@
       <c r="F7" s="4"/>
       <c r="G7" s="8"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -2092,7 +2257,7 @@
       <c r="F8" s="11"/>
       <c r="G8" s="8"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -2101,7 +2266,7 @@
       <c r="F9" s="11"/>
       <c r="G9" s="8"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="5">
         <v>9</v>
       </c>
@@ -2109,7 +2274,7 @@
       <c r="E10" s="7"/>
       <c r="G10" s="8"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -2118,59 +2283,59 @@
       <c r="F11" s="3"/>
       <c r="G11" s="8"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="G12" s="8"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="G13" s="8"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="3"/>
       <c r="G14" s="8"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="12"/>
       <c r="G15" s="8"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
       <c r="F16" s="3"/>
       <c r="G16" s="8"/>
     </row>
-    <row r="17" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
       <c r="G17" s="8"/>
     </row>
-    <row r="18" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
       <c r="G18" s="8"/>
     </row>
-    <row r="19" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
       <c r="G19" s="8"/>
     </row>
-    <row r="20" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
       <c r="G20" s="8"/>
     </row>
-    <row r="21" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="4:7" x14ac:dyDescent="0.35">
       <c r="G21" s="8"/>
     </row>
-    <row r="22" spans="4:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="4:7" x14ac:dyDescent="0.35">
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
       <c r="G22" s="8"/>

--- a/competition/專題競賽資訊.xlsx
+++ b/competition/專題競賽資訊.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Xuan\SaveMyBook\competition\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\OneDrive\文件\SaveMyBook\competition\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C27E4DD5-14DB-4056-9A0F-EC4ECF752994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B021CC0-EBBD-4261-8B10-54028297C51B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{285F9FD4-B296-469E-ADA7-FB304A9A05A2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{285F9FD4-B296-469E-ADA7-FB304A9A05A2}"/>
   </bookViews>
   <sheets>
     <sheet name="2025年相關競賽" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="191">
   <si>
     <t>競賽名稱</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -630,9 +630,6 @@
     <t>2025第30屆大專校院資訊應用服務創新競賽</t>
   </si>
   <si>
-    <t>2026第31屆大專校院資訊應用服務創新競賽</t>
-  </si>
-  <si>
     <t>萬潤2026創新創意競賽</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -681,9 +678,6 @@
     <t>2026全國大專院校產學創新實作競賽</t>
   </si>
   <si>
-    <t>2026/9/1(二)~2026/12/1(二)</t>
-  </si>
-  <si>
     <t>2025第六屆高科盃全國商業智慧競賽</t>
   </si>
   <si>
@@ -697,9 +691,6 @@
 決賽：國立高雄科技大學</t>
   </si>
   <si>
-    <t>2026/8/3(一)~2026/10/5(一)</t>
-  </si>
-  <si>
     <t>初賽：書面審查
 決賽：國立臺灣大學綜合體育館</t>
   </si>
@@ -709,10 +700,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>2026/9/1(二)~2026/10/22(四)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>~2026/10/28(三)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -783,11 +770,6 @@
     <t>https://3goodai.fgu.edu.tw/</t>
   </si>
   <si>
-    <t>初賽：書面審查
-成果展示暨頒獎典禮：佛光大學雲五館一樓藍海區</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>初賽：2026/10/13(二)~2026/10/23(五)
 決賽：2026/11/7(六)</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -813,11 +795,62 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>2026/10/01(四)~2026/11/30(一)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>https://enger.thu.edu.tw/info-on-home-page/2026%e6%99%ba%e6%85%a7%e6%b0%b8%e7%ba%8c%e5%be%aa%e7%92%b0%e6%8a%80%e8%a1%93%e7%a0%94%e8%a8%8e%e6%9c%83%e6%9a%a8%e5%b0%88%e9%a1%8c%e7%ab%b6%e8%b3%bd/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>初賽：書面審查
+成果展示暨頒獎典禮：佛光大學</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>三好AI創新應用競賽</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026第31屆大專校院資訊應用服務創新競賽</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026 International Conference on Information Management &amp; Practice 第31届國際資訊管理曁實務研討會</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>~2026/10/5(一)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>~2026/10/22(四)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>~2026/11/30(一)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>~2026/12/1(二)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>~2026/11/8(日)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>初賽：2026/11/21(六)
+決賽：2026/12/12(六)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>初賽：書面審查
+決賽：中國文化大學 台北校區</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://trustconf.skychainnet.net/conference/IMP2026-AI-192441</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中華民國資訊管理學會、中國文化大學資管糸所</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1244,19 +1277,19 @@
     <tabColor theme="4" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultColWidth="8.92578125" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.5703125" style="5" customWidth="1"/>
-    <col min="2" max="2" width="57.640625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="28.42578125" style="6" customWidth="1"/>
-    <col min="4" max="4" width="35.35546875" style="6" customWidth="1"/>
-    <col min="5" max="5" width="22.35546875" style="6" customWidth="1"/>
-    <col min="6" max="6" width="45.5703125" style="6" customWidth="1"/>
-    <col min="7" max="7" width="123.640625" style="6" customWidth="1"/>
-    <col min="8" max="16384" width="8.92578125" style="6"/>
+    <col min="1" max="1" width="3.5546875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="57.6640625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="28.44140625" style="6" customWidth="1"/>
+    <col min="4" max="4" width="35.33203125" style="6" customWidth="1"/>
+    <col min="5" max="5" width="22.33203125" style="6" customWidth="1"/>
+    <col min="6" max="6" width="45.5546875" style="6" customWidth="1"/>
+    <col min="7" max="7" width="123.6640625" style="6" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>68</v>
       </c>
@@ -1279,7 +1312,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -1302,7 +1335,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -1325,7 +1358,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -1348,7 +1381,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -1371,7 +1404,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -1394,7 +1427,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -1417,7 +1450,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -1440,7 +1473,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="31" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -1463,7 +1496,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="46.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>9</v>
       </c>
@@ -1486,7 +1519,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="31" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -1509,12 +1542,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="31" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>21</v>
@@ -1532,7 +1565,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="31" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>12</v>
       </c>
@@ -1555,7 +1588,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="31" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>13</v>
       </c>
@@ -1578,7 +1611,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="31" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>14</v>
       </c>
@@ -1601,7 +1634,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="46.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>15</v>
       </c>
@@ -1624,7 +1657,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="31" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>16</v>
       </c>
@@ -1647,7 +1680,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="31" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>17</v>
       </c>
@@ -1670,7 +1703,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="31" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>18</v>
       </c>
@@ -1693,7 +1726,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>19</v>
       </c>
@@ -1716,12 +1749,12 @@
         <v>106</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="31" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>20</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>107</v>
@@ -1739,7 +1772,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>21</v>
       </c>
@@ -1762,7 +1795,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="31" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>22</v>
       </c>
@@ -1820,20 +1853,20 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultColWidth="8.92578125" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:G24"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="48.35546875" style="6" customWidth="1"/>
-    <col min="3" max="3" width="26.92578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="33.0703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="38.0703125" style="6" customWidth="1"/>
-    <col min="6" max="6" width="42.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="52" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.92578125" style="6"/>
+    <col min="2" max="2" width="54" style="6" customWidth="1"/>
+    <col min="3" max="3" width="26.88671875" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="38.109375" style="6" customWidth="1"/>
+    <col min="6" max="6" width="42.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="247.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>68</v>
       </c>
@@ -1856,15 +1889,15 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>1</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>132</v>
@@ -1879,21 +1912,21 @@
         <v>134</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>136</v>
+        <v>180</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>154</v>
+        <v>182</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F3" s="11" t="s">
         <v>86</v>
@@ -1902,251 +1935,273 @@
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>157</v>
+        <v>183</v>
       </c>
       <c r="D4" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="F4" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="F4" s="6" t="s">
-        <v>144</v>
-      </c>
       <c r="G4" s="8" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="31" x14ac:dyDescent="0.35">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>151</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>158</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>153</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>23</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="31" x14ac:dyDescent="0.35">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>164</v>
+      <c r="B6" s="7" t="s">
+        <v>181</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>166</v>
+        <v>187</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>180</v>
+        <v>188</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>190</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="31" x14ac:dyDescent="0.35">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="B7" s="17" t="s">
-        <v>168</v>
+      <c r="B7" s="6" t="s">
+        <v>160</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>171</v>
+        <v>163</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>175</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="46.5" x14ac:dyDescent="0.35">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>7</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>90</v>
+      <c r="B8" s="17" t="s">
+        <v>164</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="46.5" x14ac:dyDescent="0.35">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>149</v>
+        <v>184</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>139</v>
+        <v>172</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>140</v>
+        <v>178</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="31" x14ac:dyDescent="0.35">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="F10" t="s">
-        <v>161</v>
+        <v>139</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>174</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B11" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="F11" t="s">
+        <v>157</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>11</v>
       </c>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="8"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="6"/>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
+      <c r="F13" s="3"/>
       <c r="G13" s="8"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="G14" s="8"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
-      <c r="F15" s="3"/>
       <c r="G15" s="8"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
-      <c r="F16" s="12"/>
+      <c r="F16" s="3"/>
       <c r="G16" s="8"/>
     </row>
-    <row r="17" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
-      <c r="F17" s="3"/>
+      <c r="F17" s="12"/>
       <c r="G17" s="8"/>
     </row>
-    <row r="18" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
+      <c r="F18" s="3"/>
       <c r="G18" s="8"/>
     </row>
-    <row r="19" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
       <c r="G19" s="8"/>
     </row>
-    <row r="20" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
       <c r="G20" s="8"/>
     </row>
-    <row r="21" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
       <c r="G21" s="8"/>
     </row>
-    <row r="22" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
       <c r="G22" s="8"/>
     </row>
-    <row r="23" spans="4:7" x14ac:dyDescent="0.35">
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
+    <row r="23" spans="4:7" x14ac:dyDescent="0.25">
       <c r="G23" s="8"/>
+    </row>
+    <row r="24" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="G24" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" xr:uid="{158A5F4F-C97E-4089-BA50-5616D4DCBAA0}"/>
     <hyperlink ref="G3" r:id="rId2" xr:uid="{DAF3C5B5-44BA-49AD-BA99-9161CE381FE1}"/>
-    <hyperlink ref="G9" r:id="rId3" xr:uid="{A143AFB3-8A14-4C9E-BBDF-4382164F17B0}"/>
+    <hyperlink ref="G10" r:id="rId3" xr:uid="{A143AFB3-8A14-4C9E-BBDF-4382164F17B0}"/>
     <hyperlink ref="G4" r:id="rId4" xr:uid="{D05275B6-E52E-4EF6-8D12-5044F28A05C2}"/>
     <hyperlink ref="G5" r:id="rId5" xr:uid="{48C0A51C-961F-4E15-A1C3-4884853F2424}"/>
-    <hyperlink ref="G10" r:id="rId6" xr:uid="{8577FF30-EE87-46EC-A8B9-6588335C2AC6}"/>
-    <hyperlink ref="G6" r:id="rId7" xr:uid="{15128193-11BE-4EA7-A0D1-AAE7972DCD68}"/>
+    <hyperlink ref="G11" r:id="rId6" xr:uid="{8577FF30-EE87-46EC-A8B9-6588335C2AC6}"/>
+    <hyperlink ref="G7" r:id="rId7" xr:uid="{15128193-11BE-4EA7-A0D1-AAE7972DCD68}"/>
+    <hyperlink ref="G6" r:id="rId8" xr:uid="{AF506C34-092A-4381-86CC-6649056D3E72}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId8"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId9"/>
 </worksheet>
 </file>
 
@@ -2156,19 +2211,19 @@
     <tabColor theme="4"/>
   </sheetPr>
   <dimension ref="A1:G22"/>
-  <sheetFormatPr defaultColWidth="8.92578125" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.5703125" style="5" customWidth="1"/>
-    <col min="2" max="2" width="57.640625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="28.42578125" style="6" customWidth="1"/>
-    <col min="4" max="4" width="35.35546875" style="6" customWidth="1"/>
-    <col min="5" max="5" width="22.35546875" style="6" customWidth="1"/>
-    <col min="6" max="6" width="45.5703125" style="6" customWidth="1"/>
-    <col min="7" max="7" width="123.640625" style="6" customWidth="1"/>
-    <col min="8" max="16384" width="8.92578125" style="6"/>
+    <col min="1" max="1" width="3.5546875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="57.6640625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="28.44140625" style="6" customWidth="1"/>
+    <col min="4" max="4" width="35.33203125" style="6" customWidth="1"/>
+    <col min="5" max="5" width="22.33203125" style="6" customWidth="1"/>
+    <col min="6" max="6" width="45.5546875" style="6" customWidth="1"/>
+    <col min="7" max="7" width="123.6640625" style="6" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>68</v>
       </c>
@@ -2191,7 +2246,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -2205,7 +2260,7 @@
       </c>
       <c r="G2" s="8"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -2214,7 +2269,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="8"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -2222,7 +2277,7 @@
       <c r="F4" s="10"/>
       <c r="G4" s="8"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -2230,7 +2285,7 @@
       <c r="E5" s="7"/>
       <c r="G5" s="8"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -2239,7 +2294,7 @@
       <c r="F6" s="3"/>
       <c r="G6" s="8"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -2248,7 +2303,7 @@
       <c r="F7" s="4"/>
       <c r="G7" s="8"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -2257,7 +2312,7 @@
       <c r="F8" s="11"/>
       <c r="G8" s="8"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -2266,7 +2321,7 @@
       <c r="F9" s="11"/>
       <c r="G9" s="8"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>9</v>
       </c>
@@ -2274,7 +2329,7 @@
       <c r="E10" s="7"/>
       <c r="G10" s="8"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -2283,59 +2338,59 @@
       <c r="F11" s="3"/>
       <c r="G11" s="8"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="G12" s="8"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="G13" s="8"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="3"/>
       <c r="G14" s="8"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="12"/>
       <c r="G15" s="8"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
       <c r="F16" s="3"/>
       <c r="G16" s="8"/>
     </row>
-    <row r="17" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
       <c r="G17" s="8"/>
     </row>
-    <row r="18" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
       <c r="G18" s="8"/>
     </row>
-    <row r="19" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
       <c r="G19" s="8"/>
     </row>
-    <row r="20" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
       <c r="G20" s="8"/>
     </row>
-    <row r="21" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="4:7" x14ac:dyDescent="0.25">
       <c r="G21" s="8"/>
     </row>
-    <row r="22" spans="4:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
       <c r="G22" s="8"/>

--- a/competition/專題競賽資訊.xlsx
+++ b/competition/專題競賽資訊.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\OneDrive\文件\SaveMyBook\competition\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B021CC0-EBBD-4261-8B10-54028297C51B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A47BE2CC-3FC0-451F-B5FB-A632961E2C89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{285F9FD4-B296-469E-ADA7-FB304A9A05A2}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="185">
   <si>
     <t>競賽名稱</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -812,10 +812,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>2026 International Conference on Information Management &amp; Practice 第31届國際資訊管理曁實務研討會</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>~2026/10/5(一)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -829,28 +825,6 @@
   </si>
   <si>
     <t>~2026/12/1(二)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>~2026/11/8(日)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>初賽：2026/11/21(六)
-決賽：2026/12/12(六)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>初賽：書面審查
-決賽：中國文化大學 台北校區</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://trustconf.skychainnet.net/conference/IMP2026-AI-192441</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>中華民國資訊管理學會、中國文化大學資管糸所</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1853,7 +1827,7 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" style="5" bestFit="1" customWidth="1"/>
@@ -1920,7 +1894,7 @@
         <v>180</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>171</v>
@@ -1943,7 +1917,7 @@
         <v>147</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>141</v>
@@ -1985,150 +1959,132 @@
       <c r="A6" s="5">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>181</v>
+      <c r="B6" s="6" t="s">
+        <v>160</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>186</v>
+        <v>161</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>187</v>
+        <v>162</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>190</v>
+        <v>163</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>175</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>160</v>
+      <c r="B7" s="17" t="s">
+        <v>164</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>175</v>
+        <v>168</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>167</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>7</v>
       </c>
-      <c r="B8" s="17" t="s">
-        <v>164</v>
+      <c r="B8" s="6" t="s">
+        <v>179</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>179</v>
+        <v>145</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>184</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>172</v>
+        <v>138</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>178</v>
+        <v>139</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>185</v>
+        <v>155</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>174</v>
+        <v>156</v>
+      </c>
+      <c r="F10" t="s">
+        <v>157</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>10</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="F11" t="s">
-        <v>157</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>176</v>
-      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="5">
-        <v>11</v>
-      </c>
+      <c r="A12" s="6"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="8"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="6"/>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
-      <c r="F13" s="3"/>
       <c r="G13" s="8"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -2139,24 +2095,24 @@
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
+      <c r="F15" s="3"/>
       <c r="G15" s="8"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
-      <c r="F16" s="3"/>
+      <c r="F16" s="12"/>
       <c r="G16" s="8"/>
     </row>
     <row r="17" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
-      <c r="F17" s="12"/>
+      <c r="F17" s="3"/>
       <c r="G17" s="8"/>
     </row>
     <row r="18" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
-      <c r="F18" s="3"/>
       <c r="G18" s="8"/>
     </row>
     <row r="19" spans="4:7" x14ac:dyDescent="0.25">
@@ -2172,36 +2128,30 @@
     <row r="21" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
       <c r="G21" s="8"/>
     </row>
     <row r="22" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
       <c r="G22" s="8"/>
     </row>
     <row r="23" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
       <c r="G23" s="8"/>
-    </row>
-    <row r="24" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="G24" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" xr:uid="{158A5F4F-C97E-4089-BA50-5616D4DCBAA0}"/>
     <hyperlink ref="G3" r:id="rId2" xr:uid="{DAF3C5B5-44BA-49AD-BA99-9161CE381FE1}"/>
-    <hyperlink ref="G10" r:id="rId3" xr:uid="{A143AFB3-8A14-4C9E-BBDF-4382164F17B0}"/>
+    <hyperlink ref="G9" r:id="rId3" xr:uid="{A143AFB3-8A14-4C9E-BBDF-4382164F17B0}"/>
     <hyperlink ref="G4" r:id="rId4" xr:uid="{D05275B6-E52E-4EF6-8D12-5044F28A05C2}"/>
     <hyperlink ref="G5" r:id="rId5" xr:uid="{48C0A51C-961F-4E15-A1C3-4884853F2424}"/>
-    <hyperlink ref="G11" r:id="rId6" xr:uid="{8577FF30-EE87-46EC-A8B9-6588335C2AC6}"/>
-    <hyperlink ref="G7" r:id="rId7" xr:uid="{15128193-11BE-4EA7-A0D1-AAE7972DCD68}"/>
-    <hyperlink ref="G6" r:id="rId8" xr:uid="{AF506C34-092A-4381-86CC-6649056D3E72}"/>
+    <hyperlink ref="G10" r:id="rId6" xr:uid="{8577FF30-EE87-46EC-A8B9-6588335C2AC6}"/>
+    <hyperlink ref="G6" r:id="rId7" xr:uid="{15128193-11BE-4EA7-A0D1-AAE7972DCD68}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId9"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId8"/>
 </worksheet>
 </file>
 

--- a/competition/專題競賽資訊.xlsx
+++ b/competition/專題競賽資訊.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\OneDrive\文件\SaveMyBook\competition\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\benj1\Documents\SaveMyBook\competition\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A47BE2CC-3FC0-451F-B5FB-A632961E2C89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B35A419A-BC10-4102-BF7E-C10640519FB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{285F9FD4-B296-469E-ADA7-FB304A9A05A2}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" activeTab="1" xr2:uid="{285F9FD4-B296-469E-ADA7-FB304A9A05A2}"/>
   </bookViews>
   <sheets>
     <sheet name="2025年相關競賽" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="188">
   <si>
     <t>競賽名稱</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -421,7 +421,7 @@
       <rPr>
         <sz val="12"/>
         <color theme="1"/>
-        <rFont val="微軟正黑體"/>
+        <rFont val="Microsoft JhengHei"/>
         <family val="2"/>
         <charset val="136"/>
         <scheme val="minor"/>
@@ -437,7 +437,7 @@
       <rPr>
         <sz val="12"/>
         <color theme="1"/>
-        <rFont val="微軟正黑體"/>
+        <rFont val="Microsoft JhengHei"/>
         <family val="2"/>
         <charset val="136"/>
         <scheme val="minor"/>
@@ -684,9 +684,6 @@
     <t>第七屆高科盃全國商業智慧競賽</t>
   </si>
   <si>
-    <t>https://ic.dxing888.com/</t>
-  </si>
-  <si>
     <t>初賽：書面審查
 決賽：國立高雄科技大學</t>
   </si>
@@ -791,14 +788,6 @@
     <t>東海大學</t>
   </si>
   <si>
-    <t>https://im.lhu.edu.tw/p/405-1010-26806,c1211.php?Lang=zh-tw</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://enger.thu.edu.tw/info-on-home-page/2026%e6%99%ba%e6%85%a7%e6%b0%b8%e7%ba%8c%e5%be%aa%e7%92%b0%e6%8a%80%e8%a1%93%e7%a0%94%e8%a8%8e%e6%9c%83%e6%9a%a8%e5%b0%88%e9%a1%8c%e7%ab%b6%e8%b3%bd/</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>初賽：書面審查
 成果展示暨頒獎典禮：佛光大學</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -826,17 +815,35 @@
   <si>
     <t>~2026/12/1(二)</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://cpt.ic.nkust.edu.tw/</t>
+  </si>
+  <si>
+    <t>數位發展部數位產業署、教育部資訊及科技教育司、中華民國資訊管理學會</t>
+  </si>
+  <si>
+    <t>https://reurl.cc/8YMr87</t>
+  </si>
+  <si>
+    <t>獎金</t>
+  </si>
+  <si>
+    <t>得獎獎項/名次</t>
+  </si>
+  <si>
+    <t>https://im.lhu.edu.tw/p/412-1010-1508.php?Lang=zh-tw</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="微軟正黑體"/>
+      <name val="Microsoft JhengHei"/>
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
@@ -845,14 +852,14 @@
       <b/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="微軟正黑體"/>
+      <name val="Microsoft JhengHei"/>
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="微軟正黑體"/>
+      <name val="Microsoft JhengHei"/>
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
@@ -861,7 +868,7 @@
       <u/>
       <sz val="12"/>
       <color theme="10"/>
-      <name val="微軟正黑體"/>
+      <name val="Microsoft JhengHei"/>
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
@@ -869,7 +876,7 @@
     <font>
       <sz val="12"/>
       <color rgb="FF333333"/>
-      <name val="微軟正黑體"/>
+      <name val="Microsoft JhengHei"/>
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
@@ -877,7 +884,7 @@
     <font>
       <sz val="12"/>
       <color rgb="FF18212B"/>
-      <name val="微軟正黑體"/>
+      <name val="Microsoft JhengHei"/>
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
@@ -885,7 +892,7 @@
     <font>
       <sz val="12"/>
       <color rgb="FF212121"/>
-      <name val="微軟正黑體"/>
+      <name val="Microsoft JhengHei"/>
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
@@ -893,7 +900,7 @@
     <font>
       <sz val="12"/>
       <color rgb="FF212529"/>
-      <name val="微軟正黑體"/>
+      <name val="Microsoft JhengHei"/>
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
@@ -902,7 +909,7 @@
       <strike/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="微軟正黑體"/>
+      <name val="Microsoft JhengHei"/>
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
@@ -912,6 +919,7 @@
       <color rgb="FF262626"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="4">
@@ -951,7 +959,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1003,6 +1011,18 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1027,7 +1047,7 @@
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 佈景主題">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="自訂 3">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1059,10 +1079,10 @@
         <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="000000"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="000000"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="自訂 3">
@@ -1251,19 +1271,19 @@
     <tabColor theme="4" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.5"/>
   <cols>
-    <col min="1" max="1" width="3.5546875" style="5" customWidth="1"/>
-    <col min="2" max="2" width="57.6640625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="28.44140625" style="6" customWidth="1"/>
-    <col min="4" max="4" width="35.33203125" style="6" customWidth="1"/>
-    <col min="5" max="5" width="22.33203125" style="6" customWidth="1"/>
-    <col min="6" max="6" width="45.5546875" style="6" customWidth="1"/>
-    <col min="7" max="7" width="123.6640625" style="6" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="6"/>
+    <col min="1" max="1" width="3.5703125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="57.640625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="28.42578125" style="6" customWidth="1"/>
+    <col min="4" max="4" width="35.35546875" style="6" customWidth="1"/>
+    <col min="5" max="5" width="22.35546875" style="6" customWidth="1"/>
+    <col min="6" max="6" width="45.5703125" style="6" customWidth="1"/>
+    <col min="7" max="7" width="123.640625" style="6" customWidth="1"/>
+    <col min="8" max="16384" width="8.85546875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="1" customFormat="1" ht="16">
       <c r="A1" s="2" t="s">
         <v>68</v>
       </c>
@@ -1286,7 +1306,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="31">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -1309,7 +1329,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="31">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -1332,7 +1352,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="31">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -1355,7 +1375,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -1378,7 +1398,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="31">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -1401,7 +1421,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="31">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -1424,7 +1444,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="31">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -1447,7 +1467,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="31">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -1470,7 +1490,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="46.5">
       <c r="A10" s="5">
         <v>9</v>
       </c>
@@ -1493,7 +1513,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="31">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -1516,7 +1536,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="31">
       <c r="A12" s="5">
         <v>11</v>
       </c>
@@ -1539,7 +1559,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="31">
       <c r="A13" s="5">
         <v>12</v>
       </c>
@@ -1562,7 +1582,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="31">
       <c r="A14" s="5">
         <v>13</v>
       </c>
@@ -1585,7 +1605,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="31">
       <c r="A15" s="5">
         <v>14</v>
       </c>
@@ -1608,7 +1628,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="46.5">
       <c r="A16" s="5">
         <v>15</v>
       </c>
@@ -1631,7 +1651,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="31">
       <c r="A17" s="5">
         <v>16</v>
       </c>
@@ -1654,7 +1674,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="31">
       <c r="A18" s="5">
         <v>17</v>
       </c>
@@ -1677,7 +1697,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="31">
       <c r="A19" s="5">
         <v>18</v>
       </c>
@@ -1700,7 +1720,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7">
       <c r="A20" s="5">
         <v>19</v>
       </c>
@@ -1723,7 +1743,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="31">
       <c r="A21" s="5">
         <v>20</v>
       </c>
@@ -1746,7 +1766,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7">
       <c r="A22" s="5">
         <v>21</v>
       </c>
@@ -1769,7 +1789,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="31">
       <c r="A23" s="5">
         <v>22</v>
       </c>
@@ -1827,20 +1847,22 @@
   <sheetPr>
     <tabColor theme="4"/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I23"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.5"/>
   <cols>
     <col min="1" max="1" width="3" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="54" style="6" customWidth="1"/>
-    <col min="3" max="3" width="26.88671875" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="33.109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="38.109375" style="6" customWidth="1"/>
-    <col min="6" max="6" width="42.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="247.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="6"/>
+    <col min="2" max="2" width="49.640625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="15.35546875" style="6" customWidth="1"/>
+    <col min="4" max="4" width="33.140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30" style="6" customWidth="1"/>
+    <col min="6" max="6" width="24.640625" style="6" customWidth="1"/>
+    <col min="7" max="7" width="54.2109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.640625" style="6" customWidth="1"/>
+    <col min="9" max="9" width="9.42578125" style="6" customWidth="1"/>
+    <col min="10" max="16384" width="8.85546875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="1" customFormat="1" ht="16">
       <c r="A1" s="2" t="s">
         <v>68</v>
       </c>
@@ -1862,8 +1884,14 @@
       <c r="G1" s="1" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="H1" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="31">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -1886,38 +1914,38 @@
         <v>134</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="31">
       <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>180</v>
+      <c r="B3" s="19" t="s">
+        <v>177</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>86</v>
+        <v>151</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>183</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="31">
       <c r="A4" s="5">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="19" t="s">
         <v>147</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>141</v>
@@ -1932,107 +1960,107 @@
         <v>140</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="31">
       <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="20" t="s">
         <v>149</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>23</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="31">
       <c r="A6" s="5">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="E6" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="E6" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>175</v>
+      <c r="F6" s="17" t="s">
+        <v>174</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="31">
       <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="D7" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="E7" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="G7" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="F7" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:9" ht="31">
       <c r="A8" s="5">
         <v>7</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>179</v>
+      <c r="B8" s="19" t="s">
+        <v>176</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D8" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="E8" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>173</v>
-      </c>
       <c r="G8" s="8" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="31">
       <c r="A9" s="5">
         <v>8</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="19" t="s">
         <v>145</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>138</v>
@@ -2040,101 +2068,101 @@
       <c r="E9" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="F9" s="11" t="s">
-        <v>174</v>
+      <c r="F9" s="3" t="s">
+        <v>173</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="31">
       <c r="A10" s="5">
         <v>9</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>159</v>
+      <c r="B10" s="19" t="s">
+        <v>158</v>
       </c>
       <c r="C10" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="E10" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="E10" s="7" t="s">
+      <c r="F10" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="F10" t="s">
-        <v>157</v>
-      </c>
       <c r="G10" s="8" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9">
       <c r="A12" s="6"/>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="F12" s="3"/>
       <c r="G12" s="8"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9">
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="G13" s="8"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9">
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="G14" s="8"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9">
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="3"/>
       <c r="G15" s="8"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9">
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
       <c r="F16" s="12"/>
       <c r="G16" s="8"/>
     </row>
-    <row r="17" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="4:7">
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
       <c r="F17" s="3"/>
       <c r="G17" s="8"/>
     </row>
-    <row r="18" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:7">
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
       <c r="G18" s="8"/>
     </row>
-    <row r="19" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="4:7">
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
       <c r="G19" s="8"/>
     </row>
-    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:7">
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
       <c r="G20" s="8"/>
     </row>
-    <row r="21" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="4:7">
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
       <c r="F21" s="7"/>
       <c r="G21" s="8"/>
     </row>
-    <row r="22" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="4:7">
       <c r="G22" s="8"/>
     </row>
-    <row r="23" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="4:7">
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
       <c r="G23" s="8"/>
@@ -2149,9 +2177,11 @@
     <hyperlink ref="G5" r:id="rId5" xr:uid="{48C0A51C-961F-4E15-A1C3-4884853F2424}"/>
     <hyperlink ref="G10" r:id="rId6" xr:uid="{8577FF30-EE87-46EC-A8B9-6588335C2AC6}"/>
     <hyperlink ref="G6" r:id="rId7" xr:uid="{15128193-11BE-4EA7-A0D1-AAE7972DCD68}"/>
+    <hyperlink ref="G7" r:id="rId8" xr:uid="{590F66A8-495F-4CF3-AEA5-273ECFEE87C0}"/>
+    <hyperlink ref="G8" r:id="rId9" xr:uid="{85A35B9E-926B-49C4-A082-465C4C78D0CF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId8"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId10"/>
 </worksheet>
 </file>
 
@@ -2161,19 +2191,19 @@
     <tabColor theme="4"/>
   </sheetPr>
   <dimension ref="A1:G22"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.5"/>
   <cols>
-    <col min="1" max="1" width="3.5546875" style="5" customWidth="1"/>
-    <col min="2" max="2" width="57.6640625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="28.44140625" style="6" customWidth="1"/>
-    <col min="4" max="4" width="35.33203125" style="6" customWidth="1"/>
-    <col min="5" max="5" width="22.33203125" style="6" customWidth="1"/>
-    <col min="6" max="6" width="45.5546875" style="6" customWidth="1"/>
-    <col min="7" max="7" width="123.6640625" style="6" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="6"/>
+    <col min="1" max="1" width="3.5703125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="57.640625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="28.42578125" style="6" customWidth="1"/>
+    <col min="4" max="4" width="35.35546875" style="6" customWidth="1"/>
+    <col min="5" max="5" width="22.35546875" style="6" customWidth="1"/>
+    <col min="6" max="6" width="45.5703125" style="6" customWidth="1"/>
+    <col min="7" max="7" width="123.640625" style="6" customWidth="1"/>
+    <col min="8" max="16384" width="8.85546875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="1" customFormat="1" ht="16">
       <c r="A1" s="2" t="s">
         <v>68</v>
       </c>
@@ -2196,7 +2226,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -2210,7 +2240,7 @@
       </c>
       <c r="G2" s="8"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -2219,7 +2249,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="8"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -2227,7 +2257,7 @@
       <c r="F4" s="10"/>
       <c r="G4" s="8"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -2235,7 +2265,7 @@
       <c r="E5" s="7"/>
       <c r="G5" s="8"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -2244,7 +2274,7 @@
       <c r="F6" s="3"/>
       <c r="G6" s="8"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -2253,7 +2283,7 @@
       <c r="F7" s="4"/>
       <c r="G7" s="8"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -2262,7 +2292,7 @@
       <c r="F8" s="11"/>
       <c r="G8" s="8"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -2271,7 +2301,7 @@
       <c r="F9" s="11"/>
       <c r="G9" s="8"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7">
       <c r="A10" s="5">
         <v>9</v>
       </c>
@@ -2279,7 +2309,7 @@
       <c r="E10" s="7"/>
       <c r="G10" s="8"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -2288,59 +2318,59 @@
       <c r="F11" s="3"/>
       <c r="G11" s="8"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7">
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="G12" s="8"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7">
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="G13" s="8"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7">
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="3"/>
       <c r="G14" s="8"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7">
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="12"/>
       <c r="G15" s="8"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7">
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
       <c r="F16" s="3"/>
       <c r="G16" s="8"/>
     </row>
-    <row r="17" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="4:7">
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
       <c r="G17" s="8"/>
     </row>
-    <row r="18" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:7">
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
       <c r="G18" s="8"/>
     </row>
-    <row r="19" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="4:7">
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
       <c r="G19" s="8"/>
     </row>
-    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:7">
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
       <c r="G20" s="8"/>
     </row>
-    <row r="21" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="4:7">
       <c r="G21" s="8"/>
     </row>
-    <row r="22" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="4:7">
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
       <c r="G22" s="8"/>
